--- a/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_edad.xlsx
+++ b/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_edad.xlsx
@@ -104,10 +104,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>0.40863072872161865</v>
+        <v>0.47360128164291382</v>
       </c>
       <c r="D2" s="1">
-        <v>40.863071441650391</v>
+        <v>47.360126495361328</v>
       </c>
     </row>
     <row r="3">
@@ -118,10 +118,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>0.46869757771492004</v>
+        <v>0.49506074190139771</v>
       </c>
       <c r="D3" s="1">
-        <v>46.869758605957031</v>
+        <v>49.506072998046875</v>
       </c>
     </row>
     <row r="4">
@@ -132,10 +132,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="1">
-        <v>0.55095982551574707</v>
+        <v>0.57638376951217651</v>
       </c>
       <c r="D4" s="1">
-        <v>55.095981597900391</v>
+        <v>57.638378143310547</v>
       </c>
     </row>
     <row r="5">
@@ -146,10 +146,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>0.39509111642837524</v>
+        <v>0.42061451077461243</v>
       </c>
       <c r="D5" s="1">
-        <v>39.509113311767578</v>
+        <v>42.061450958251953</v>
       </c>
     </row>
     <row r="6">
@@ -160,10 +160,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>0.43438789248466492</v>
+        <v>0.44646444916725159</v>
       </c>
       <c r="D6" s="1">
-        <v>43.438789367675781</v>
+        <v>44.646446228027344</v>
       </c>
     </row>
     <row r="7">
@@ -174,10 +174,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>0.54092490673065186</v>
+        <v>0.55965536832809448</v>
       </c>
       <c r="D7" s="1">
-        <v>54.092491149902344</v>
+        <v>55.965538024902344</v>
       </c>
     </row>
     <row r="8">
@@ -188,10 +188,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>0.28347775340080261</v>
+        <v>0.33319205045700073</v>
       </c>
       <c r="D8" s="1">
-        <v>28.347774505615234</v>
+        <v>33.319206237792969</v>
       </c>
     </row>
     <row r="9">
@@ -202,10 +202,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>0.31386852264404297</v>
+        <v>0.33484914898872376</v>
       </c>
       <c r="D9" s="1">
-        <v>31.386852264404297</v>
+        <v>33.484916687011719</v>
       </c>
     </row>
     <row r="10">
@@ -216,10 +216,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="1">
-        <v>0.4017217755317688</v>
+        <v>0.42849981784820557</v>
       </c>
       <c r="D10" s="1">
-        <v>40.172176361083984</v>
+        <v>42.849983215332031</v>
       </c>
     </row>
     <row r="11">
@@ -230,10 +230,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>0.21840198338031769</v>
+        <v>0.27056005597114563</v>
       </c>
       <c r="D11" s="1">
-        <v>21.840198516845703</v>
+        <v>27.056005477905274</v>
       </c>
     </row>
     <row r="12">
@@ -244,10 +244,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="1">
-        <v>0.25709757208824158</v>
+        <v>0.28504574298858643</v>
       </c>
       <c r="D12" s="1">
-        <v>25.709756851196289</v>
+        <v>28.504573822021484</v>
       </c>
     </row>
     <row r="13">
@@ -258,10 +258,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="1">
-        <v>0.35892260074615479</v>
+        <v>0.39233797788619995</v>
       </c>
       <c r="D13" s="1">
-        <v>35.892261505126953</v>
+        <v>39.233798980712891</v>
       </c>
     </row>
     <row r="14">
@@ -272,10 +272,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>0.20117029547691345</v>
+        <v>0.24724121391773224</v>
       </c>
       <c r="D14" s="1">
-        <v>20.117029190063477</v>
+        <v>24.72412109375</v>
       </c>
     </row>
     <row r="15">
@@ -286,10 +286,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>0.2371431440114975</v>
+        <v>0.26178574562072754</v>
       </c>
       <c r="D15" s="1">
-        <v>23.714313507080078</v>
+        <v>26.178573608398438</v>
       </c>
     </row>
     <row r="16">
@@ -300,10 +300,10 @@
         <v>4</v>
       </c>
       <c r="C16" s="1">
-        <v>0.30009794235229492</v>
+        <v>0.33485183119773865</v>
       </c>
       <c r="D16" s="1">
-        <v>30.009794235229492</v>
+        <v>33.485183715820313</v>
       </c>
     </row>
     <row r="17">
@@ -314,10 +314,10 @@
         <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>0.19679832458496094</v>
+        <v>0.25769084692001343</v>
       </c>
       <c r="D17" s="1">
-        <v>19.679832458496094</v>
+        <v>25.769084930419922</v>
       </c>
     </row>
     <row r="18">
@@ -328,10 +328,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="1">
-        <v>0.24774070084095001</v>
+        <v>0.27679538726806641</v>
       </c>
       <c r="D18" s="1">
-        <v>24.774070739746094</v>
+        <v>27.679538726806641</v>
       </c>
     </row>
     <row r="19">
@@ -342,10 +342,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="1">
-        <v>0.30143952369689941</v>
+        <v>0.33337113261222839</v>
       </c>
       <c r="D19" s="1">
-        <v>30.143951416015625</v>
+        <v>33.337112426757813</v>
       </c>
     </row>
     <row r="20">
@@ -356,10 +356,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>0.15995542705059052</v>
+        <v>0.21364806592464447</v>
       </c>
       <c r="D20" s="1">
-        <v>15.995542526245117</v>
+        <v>21.36480712890625</v>
       </c>
     </row>
     <row r="21">
@@ -370,10 +370,10 @@
         <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>0.2188158929347992</v>
+        <v>0.24740317463874817</v>
       </c>
       <c r="D21" s="1">
-        <v>21.881589889526367</v>
+        <v>24.740318298339844</v>
       </c>
     </row>
     <row r="22">
@@ -384,10 +384,10 @@
         <v>4</v>
       </c>
       <c r="C22" s="1">
-        <v>0.27758052945137024</v>
+        <v>0.31107440590858459</v>
       </c>
       <c r="D22" s="1">
-        <v>27.758052825927734</v>
+        <v>31.107440948486328</v>
       </c>
     </row>
     <row r="23">
@@ -398,10 +398,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="1">
-        <v>0.14399209618568421</v>
+        <v>0.18518276512622833</v>
       </c>
       <c r="D23" s="1">
-        <v>14.399209976196289</v>
+        <v>18.518276214599609</v>
       </c>
     </row>
     <row r="24">
@@ -412,10 +412,10 @@
         <v>3</v>
       </c>
       <c r="C24" s="1">
-        <v>0.18432794511318207</v>
+        <v>0.20646224915981293</v>
       </c>
       <c r="D24" s="1">
-        <v>18.432794570922852</v>
+        <v>20.646224975585938</v>
       </c>
     </row>
     <row r="25">
@@ -426,10 +426,10 @@
         <v>4</v>
       </c>
       <c r="C25" s="1">
-        <v>0.26343488693237305</v>
+        <v>0.30326551198959351</v>
       </c>
       <c r="D25" s="1">
-        <v>26.343488693237305</v>
+        <v>30.32655143737793</v>
       </c>
     </row>
     <row r="26">
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="C26" s="1">
-        <v>0.120194211602211</v>
+        <v>0.17173412442207337</v>
       </c>
       <c r="D26" s="1">
-        <v>12.019421577453613</v>
+        <v>17.173412322998047</v>
       </c>
     </row>
     <row r="27">
@@ -454,10 +454,10 @@
         <v>3</v>
       </c>
       <c r="C27" s="1">
-        <v>0.17418774962425232</v>
+        <v>0.19938723742961884</v>
       </c>
       <c r="D27" s="1">
-        <v>17.41877555847168</v>
+        <v>19.938724517822266</v>
       </c>
     </row>
     <row r="28">
@@ -468,10 +468,10 @@
         <v>4</v>
       </c>
       <c r="C28" s="1">
-        <v>0.22858510911464691</v>
+        <v>0.28420555591583252</v>
       </c>
       <c r="D28" s="1">
-        <v>22.858510971069336</v>
+        <v>28.420555114746094</v>
       </c>
     </row>
     <row r="29">
@@ -482,10 +482,10 @@
         <v>2</v>
       </c>
       <c r="C29" s="1">
-        <v>0.11522375047206879</v>
+        <v>0.15230204164981842</v>
       </c>
       <c r="D29" s="1">
-        <v>11.522375106811523</v>
+        <v>15.230204582214355</v>
       </c>
     </row>
     <row r="30">
@@ -496,10 +496,10 @@
         <v>3</v>
       </c>
       <c r="C30" s="1">
-        <v>0.16621334850788116</v>
+        <v>0.18335093557834625</v>
       </c>
       <c r="D30" s="1">
-        <v>16.621334075927734</v>
+        <v>18.335094451904297</v>
       </c>
     </row>
     <row r="31">
@@ -510,10 +510,10 @@
         <v>4</v>
       </c>
       <c r="C31" s="1">
-        <v>0.17786654829978943</v>
+        <v>0.20588050782680512</v>
       </c>
       <c r="D31" s="1">
-        <v>17.786655426025391</v>
+        <v>20.588050842285156</v>
       </c>
     </row>
     <row r="32">
@@ -524,10 +524,10 @@
         <v>2</v>
       </c>
       <c r="C32" s="1">
-        <v>0.10418066382408142</v>
+        <v>0.14172959327697754</v>
       </c>
       <c r="D32" s="1">
-        <v>10.418066024780273</v>
+        <v>14.172959327697754</v>
       </c>
     </row>
     <row r="33">
@@ -538,10 +538,10 @@
         <v>3</v>
       </c>
       <c r="C33" s="1">
-        <v>0.14427688717842102</v>
+        <v>0.16188609600067139</v>
       </c>
       <c r="D33" s="1">
-        <v>14.427688598632813</v>
+        <v>16.188610076904297</v>
       </c>
     </row>
     <row r="34">
@@ -552,10 +552,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="1">
-        <v>0.15587911009788513</v>
+        <v>0.17970770597457886</v>
       </c>
       <c r="D34" s="1">
-        <v>15.587910652160645</v>
+        <v>17.970769882202148</v>
       </c>
     </row>
     <row r="35">
@@ -566,10 +566,10 @@
         <v>2</v>
       </c>
       <c r="C35" s="1">
-        <v>0.11505016684532166</v>
+        <v>0.15904374420642853</v>
       </c>
       <c r="D35" s="1">
-        <v>11.505016326904297</v>
+        <v>15.904374122619629</v>
       </c>
     </row>
     <row r="36">
@@ -580,10 +580,10 @@
         <v>3</v>
       </c>
       <c r="C36" s="1">
-        <v>0.14290176331996918</v>
+        <v>0.16837297379970551</v>
       </c>
       <c r="D36" s="1">
-        <v>14.290176391601563</v>
+        <v>16.837297439575195</v>
       </c>
     </row>
     <row r="37">
@@ -594,10 +594,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="1">
-        <v>0.19165743887424469</v>
+        <v>0.22265176475048065</v>
       </c>
       <c r="D37" s="1">
-        <v>19.165744781494141</v>
+        <v>22.265176773071289</v>
       </c>
     </row>
     <row r="38">
@@ -608,10 +608,10 @@
         <v>2</v>
       </c>
       <c r="C38" s="1">
-        <v>0.10696208477020264</v>
+        <v>0.16119426488876343</v>
       </c>
       <c r="D38" s="1">
-        <v>10.696208953857422</v>
+        <v>16.119426727294922</v>
       </c>
     </row>
     <row r="39">
@@ -622,10 +622,10 @@
         <v>3</v>
       </c>
       <c r="C39" s="1">
-        <v>0.15056079626083374</v>
+        <v>0.17573775351047516</v>
       </c>
       <c r="D39" s="1">
-        <v>15.056079864501953</v>
+        <v>17.573776245117188</v>
       </c>
     </row>
     <row r="40">
@@ -636,10 +636,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="1">
-        <v>0.20111159980297089</v>
+        <v>0.2398868203163147</v>
       </c>
       <c r="D40" s="1">
-        <v>20.111160278320313</v>
+        <v>23.988681793212891</v>
       </c>
     </row>
     <row r="41">
@@ -650,10 +650,10 @@
         <v>2</v>
       </c>
       <c r="C41" s="1">
-        <v>0.1071963906288147</v>
+        <v>0.15988615155220032</v>
       </c>
       <c r="D41" s="1">
-        <v>10.719638824462891</v>
+        <v>15.988615036010742</v>
       </c>
     </row>
     <row r="42">
@@ -664,10 +664,10 @@
         <v>3</v>
       </c>
       <c r="C42" s="1">
-        <v>0.13329859077930451</v>
+        <v>0.15850420296192169</v>
       </c>
       <c r="D42" s="1">
-        <v>13.329858779907227</v>
+        <v>15.850419998168945</v>
       </c>
     </row>
     <row r="43">
@@ -678,10 +678,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="1">
-        <v>0.16392737627029419</v>
+        <v>0.2015424519777298</v>
       </c>
       <c r="D43" s="1">
-        <v>16.392738342285156</v>
+        <v>20.154245376586914</v>
       </c>
     </row>
     <row r="44">
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="C44" s="1">
-        <v>0.10296738147735596</v>
+        <v>0.18551671504974365</v>
       </c>
       <c r="D44" s="1">
-        <v>10.296737670898438</v>
+        <v>18.551671981811523</v>
       </c>
     </row>
     <row r="45">
@@ -706,10 +706,10 @@
         <v>3</v>
       </c>
       <c r="C45" s="1">
-        <v>0.14834880828857422</v>
+        <v>0.18792060017585754</v>
       </c>
       <c r="D45" s="1">
-        <v>14.834880828857422</v>
+        <v>18.792060852050781</v>
       </c>
     </row>
     <row r="46">
@@ -720,10 +720,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="1">
-        <v>0.1543060839176178</v>
+        <v>0.15922829508781433</v>
       </c>
       <c r="D46" s="1">
-        <v>15.430608749389648</v>
+        <v>15.922829627990723</v>
       </c>
     </row>
     <row r="47">
@@ -734,10 +734,10 @@
         <v>2</v>
       </c>
       <c r="C47" s="1">
-        <v>0.12245285511016846</v>
+        <v>0.20099207758903504</v>
       </c>
       <c r="D47" s="1">
-        <v>12.245285034179688</v>
+        <v>20.099206924438477</v>
       </c>
     </row>
     <row r="48">
@@ -748,10 +748,10 @@
         <v>3</v>
       </c>
       <c r="C48" s="1">
-        <v>0.16017375886440277</v>
+        <v>0.19086633622646332</v>
       </c>
       <c r="D48" s="1">
-        <v>16.017375946044922</v>
+        <v>19.086633682250977</v>
       </c>
     </row>
     <row r="49">
@@ -762,10 +762,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="1">
-        <v>0.14078322052955627</v>
+        <v>0.15888561308383942</v>
       </c>
       <c r="D49" s="1">
-        <v>14.078322410583496</v>
+        <v>15.888561248779297</v>
       </c>
     </row>
     <row r="50">
@@ -776,10 +776,10 @@
         <v>2</v>
       </c>
       <c r="C50" s="1">
-        <v>0.16361519694328308</v>
+        <v>0.262006014585495</v>
       </c>
       <c r="D50" s="1">
-        <v>16.361518859863281</v>
+        <v>26.200601577758789</v>
       </c>
     </row>
     <row r="51">
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="C51" s="1">
-        <v>0.22446870803833008</v>
+        <v>0.25390821695327759</v>
       </c>
       <c r="D51" s="1">
-        <v>22.446870803833008</v>
+        <v>25.39082145690918</v>
       </c>
     </row>
     <row r="52">
@@ -804,10 +804,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="1">
-        <v>0.17554621398448944</v>
+        <v>0.20235782861709595</v>
       </c>
       <c r="D52" s="1">
-        <v>17.554620742797852</v>
+        <v>20.235782623291016</v>
       </c>
     </row>
     <row r="53">
@@ -818,10 +818,10 @@
         <v>2</v>
       </c>
       <c r="C53" s="1">
-        <v>0.14898748695850372</v>
+        <v>0.220537930727005</v>
       </c>
       <c r="D53" s="1">
-        <v>14.898748397827148</v>
+        <v>22.053792953491211</v>
       </c>
     </row>
     <row r="54">
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="C54" s="1">
-        <v>0.20066517591476441</v>
+        <v>0.22168166935443878</v>
       </c>
       <c r="D54" s="1">
-        <v>20.066516876220703</v>
+        <v>22.168167114257813</v>
       </c>
     </row>
     <row r="55">
@@ -846,10 +846,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="1">
-        <v>0.15866917371749878</v>
+        <v>0.14867858588695526</v>
       </c>
       <c r="D55" s="1">
-        <v>15.866917610168457</v>
+        <v>14.86785888671875</v>
       </c>
     </row>
     <row r="56">
@@ -860,10 +860,10 @@
         <v>2</v>
       </c>
       <c r="C56" s="1">
-        <v>0.11810549348592758</v>
+        <v>0.17053820192813873</v>
       </c>
       <c r="D56" s="1">
-        <v>11.810549736022949</v>
+        <v>17.05381965637207</v>
       </c>
     </row>
     <row r="57">
@@ -874,10 +874,10 @@
         <v>3</v>
       </c>
       <c r="C57" s="1">
-        <v>0.16816900670528412</v>
+        <v>0.19324281811714172</v>
       </c>
       <c r="D57" s="1">
-        <v>16.816900253295898</v>
+        <v>19.324281692504883</v>
       </c>
     </row>
     <row r="58">
@@ -888,10 +888,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="1">
-        <v>0.16469930112361908</v>
+        <v>0.14359559118747711</v>
       </c>
       <c r="D58" s="1">
-        <v>16.469930648803711</v>
+        <v>14.359559059143066</v>
       </c>
     </row>
     <row r="59">
@@ -902,10 +902,10 @@
         <v>2</v>
       </c>
       <c r="C59" s="1">
-        <v>0.14036144316196442</v>
+        <v>0.18485246598720551</v>
       </c>
       <c r="D59" s="1">
-        <v>14.036144256591797</v>
+        <v>18.485246658325195</v>
       </c>
     </row>
     <row r="60">
@@ -916,10 +916,10 @@
         <v>3</v>
       </c>
       <c r="C60" s="1">
-        <v>0.1624729335308075</v>
+        <v>0.19302241504192352</v>
       </c>
       <c r="D60" s="1">
-        <v>16.247293472290039</v>
+        <v>19.302242279052734</v>
       </c>
     </row>
     <row r="61">
@@ -930,10 +930,10 @@
         <v>4</v>
       </c>
       <c r="C61" s="1">
-        <v>0.16792187094688416</v>
+        <v>0.14981120824813843</v>
       </c>
       <c r="D61" s="1">
-        <v>16.792186737060547</v>
+        <v>14.981121063232422</v>
       </c>
     </row>
     <row r="62">
@@ -944,10 +944,10 @@
         <v>2</v>
       </c>
       <c r="C62" s="1">
-        <v>0.14576274156570435</v>
+        <v>0.20339830219745636</v>
       </c>
       <c r="D62" s="1">
-        <v>14.576273918151855</v>
+        <v>20.33983039855957</v>
       </c>
     </row>
     <row r="63">
@@ -958,10 +958,10 @@
         <v>3</v>
       </c>
       <c r="C63" s="1">
-        <v>0.17213462293148041</v>
+        <v>0.20707577466964722</v>
       </c>
       <c r="D63" s="1">
-        <v>17.213462829589844</v>
+        <v>20.707576751708984</v>
       </c>
     </row>
     <row r="64">
@@ -972,10 +972,10 @@
         <v>4</v>
       </c>
       <c r="C64" s="1">
-        <v>0.17526356875896454</v>
+        <v>0.15432006120681763</v>
       </c>
       <c r="D64" s="1">
-        <v>17.526357650756836</v>
+        <v>15.432005882263184</v>
       </c>
     </row>
     <row r="65">
@@ -986,10 +986,10 @@
         <v>2</v>
       </c>
       <c r="C65" s="1">
-        <v>0.097143128514289856</v>
+        <v>0.13468685746192932</v>
       </c>
       <c r="D65" s="1">
-        <v>9.7143125534057617</v>
+        <v>13.468686103820801</v>
       </c>
     </row>
     <row r="66">
@@ -1000,10 +1000,10 @@
         <v>3</v>
       </c>
       <c r="C66" s="1">
-        <v>0.15410037338733673</v>
+        <v>0.17412671446800232</v>
       </c>
       <c r="D66" s="1">
-        <v>15.410037040710449</v>
+        <v>17.41267204284668</v>
       </c>
     </row>
     <row r="67">
@@ -1014,10 +1014,10 @@
         <v>4</v>
       </c>
       <c r="C67" s="1">
-        <v>0.14016366004943848</v>
+        <v>0.10787514597177505</v>
       </c>
       <c r="D67" s="1">
-        <v>14.016366004943848</v>
+        <v>10.787514686584473</v>
       </c>
     </row>
   </sheetData>
